--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
@@ -592,25 +592,25 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>78.05</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>21.95</v>
+        <v>19.51</v>
       </c>
       <c r="I4" s="2">
         <v>7.2</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K4" s="1">
-        <v>21.95</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -624,19 +624,19 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>80.48999999999999</v>
+        <v>80</v>
       </c>
       <c r="H5" s="1">
-        <v>19.51</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2">
         <v>6.6</v>
@@ -645,7 +645,7 @@
         <v>7</v>
       </c>
       <c r="K5" s="1">
-        <v>17.07</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -799,22 +799,22 @@
         <v>27</v>
       </c>
       <c r="D10">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>92.86</v>
+        <v>93.02</v>
       </c>
       <c r="H10" s="1">
-        <v>7.14</v>
+        <v>6.98</v>
       </c>
       <c r="I10" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -869,28 +869,28 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12">
         <v>23</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>74.19</v>
+        <v>76.67</v>
       </c>
       <c r="H12" s="1">
-        <v>25.81</v>
+        <v>23.33</v>
       </c>
       <c r="I12" s="2">
         <v>7.8</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -959,22 +959,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>32.35</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.6</v>
       </c>
       <c r="J2">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -991,22 +994,25 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>35.29</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.9</v>
       </c>
       <c r="J3">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1023,22 +1029,25 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>70.73</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>29.27</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1052,25 +1061,28 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.2</v>
       </c>
       <c r="J5">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1087,22 +1099,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F6">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>47.22</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>52.78</v>
+      </c>
+      <c r="I6" s="2">
+        <v>6.7</v>
       </c>
       <c r="J6">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1119,22 +1134,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1151,22 +1169,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.9</v>
       </c>
       <c r="J8">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1183,22 +1204,25 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F9">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.9</v>
       </c>
       <c r="J9">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1212,25 +1236,28 @@
         <v>27</v>
       </c>
       <c r="D10">
+        <v>43</v>
+      </c>
+      <c r="E10">
         <v>42</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
       <c r="F10">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>97.67</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>2.33</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.9</v>
       </c>
       <c r="J10">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1247,22 +1274,25 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>56.41</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>43.59</v>
+      </c>
+      <c r="I11" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J11">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1276,13 +1306,13 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1291,7 +1321,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K12" s="1">
         <v>100</v>
@@ -1375,7 +1405,7 @@
         <v>32.35</v>
       </c>
       <c r="I2" s="2">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J2">
         <v>11</v>
@@ -1410,7 +1440,7 @@
         <v>35.29</v>
       </c>
       <c r="I3" s="2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J3">
         <v>12</v>
@@ -1445,13 +1475,13 @@
         <v>21.95</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K4" s="1">
-        <v>21.95</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1465,28 +1495,28 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5">
         <v>33</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>80.48999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="H5" s="1">
-        <v>19.51</v>
+        <v>17.5</v>
       </c>
       <c r="I5" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J5">
         <v>7</v>
       </c>
       <c r="K5" s="1">
-        <v>17.07</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1503,19 +1533,19 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1">
-        <v>63.89</v>
+        <v>58.33</v>
       </c>
       <c r="H6" s="1">
-        <v>36.11</v>
+        <v>41.67</v>
       </c>
       <c r="I6" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J6">
         <v>13</v>
@@ -1538,19 +1568,19 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1573,16 +1603,16 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>93.18000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="H8" s="1">
-        <v>6.82</v>
+        <v>4.55</v>
       </c>
       <c r="I8" s="2">
         <v>9.1</v>
@@ -1608,19 +1638,19 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>95.34999999999999</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1640,19 +1670,19 @@
         <v>27</v>
       </c>
       <c r="D10">
+        <v>43</v>
+      </c>
+      <c r="E10">
         <v>42</v>
       </c>
-      <c r="E10">
-        <v>39</v>
-      </c>
       <c r="F10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>92.86</v>
+        <v>97.67</v>
       </c>
       <c r="H10" s="1">
-        <v>7.14</v>
+        <v>2.33</v>
       </c>
       <c r="I10" s="2">
         <v>9.199999999999999</v>
@@ -1690,7 +1720,7 @@
         <v>28.21</v>
       </c>
       <c r="I11" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J11">
         <v>11</v>
@@ -1710,28 +1740,28 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E12">
         <v>23</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1">
-        <v>74.19</v>
+        <v>76.67</v>
       </c>
       <c r="H12" s="1">
-        <v>25.81</v>
+        <v>23.33</v>
       </c>
       <c r="I12" s="2">
         <v>7.8</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
@@ -1309,22 +1309,25 @@
         <v>30</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.9</v>
       </c>
       <c r="J12">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>6.67</v>
       </c>
     </row>
   </sheetData>
@@ -1743,19 +1746,19 @@
         <v>30</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>76.67</v>
+        <v>86.67</v>
       </c>
       <c r="H12" s="1">
-        <v>23.33</v>
+        <v>13.33</v>
       </c>
       <c r="I12" s="2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
@@ -1029,25 +1029,25 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>70.73</v>
+        <v>75.61</v>
       </c>
       <c r="H4" s="1">
-        <v>29.27</v>
+        <v>24.39</v>
       </c>
       <c r="I4" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K4" s="1">
-        <v>26.83</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1064,25 +1064,25 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="H5" s="1">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="I5" s="2">
         <v>6.2</v>
       </c>
       <c r="J5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K5" s="1">
-        <v>20</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1099,25 +1099,25 @@
         <v>36</v>
       </c>
       <c r="E6">
+        <v>19</v>
+      </c>
+      <c r="F6">
         <v>17</v>
       </c>
-      <c r="F6">
-        <v>19</v>
-      </c>
       <c r="G6" s="1">
+        <v>52.78</v>
+      </c>
+      <c r="H6" s="1">
         <v>47.22</v>
       </c>
-      <c r="H6" s="1">
-        <v>52.78</v>
-      </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="J6">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K6" s="1">
-        <v>47.22</v>
+        <v>36.11</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1274,25 +1274,25 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1">
-        <v>56.41</v>
+        <v>69.23</v>
       </c>
       <c r="H11" s="1">
-        <v>43.59</v>
+        <v>30.77</v>
       </c>
       <c r="I11" s="2">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J11">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K11" s="1">
-        <v>43.59</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1466,19 +1466,19 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>78.05</v>
+        <v>75.61</v>
       </c>
       <c r="H4" s="1">
-        <v>21.95</v>
+        <v>24.39</v>
       </c>
       <c r="I4" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -1536,19 +1536,19 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1">
-        <v>58.33</v>
+        <v>52.78</v>
       </c>
       <c r="H6" s="1">
-        <v>41.67</v>
+        <v>47.22</v>
       </c>
       <c r="I6" s="2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J6">
         <v>13</v>
@@ -1723,7 +1723,7 @@
         <v>28.21</v>
       </c>
       <c r="I11" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J11">
         <v>11</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
@@ -1286,13 +1286,13 @@
         <v>30.77</v>
       </c>
       <c r="I11" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K11" s="1">
-        <v>30.77</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1711,16 +1711,16 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" s="1">
-        <v>71.79000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="H11" s="1">
-        <v>28.21</v>
+        <v>30.77</v>
       </c>
       <c r="I11" s="2">
         <v>9.1</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
@@ -604,13 +604,13 @@
         <v>19.51</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>19.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -639,13 +639,13 @@
         <v>20</v>
       </c>
       <c r="I5" s="2">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -674,13 +674,13 @@
         <v>36.11</v>
       </c>
       <c r="I6" s="2">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>36.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1029,25 +1029,25 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>75.61</v>
+        <v>78.05</v>
       </c>
       <c r="H4" s="1">
-        <v>24.39</v>
+        <v>21.95</v>
       </c>
       <c r="I4" s="2">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>19.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1076,13 +1076,13 @@
         <v>17.5</v>
       </c>
       <c r="I5" s="2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1099,25 +1099,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
-        <v>52.78</v>
+        <v>61.11</v>
       </c>
       <c r="H6" s="1">
-        <v>47.22</v>
+        <v>38.89</v>
       </c>
       <c r="I6" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>36.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1466,25 +1466,25 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>75.61</v>
+        <v>78.05</v>
       </c>
       <c r="H4" s="1">
-        <v>24.39</v>
+        <v>21.95</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>19.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1513,13 +1513,13 @@
         <v>17.5</v>
       </c>
       <c r="I5" s="2">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="J5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1536,25 +1536,25 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G6" s="1">
-        <v>52.78</v>
+        <v>61.11</v>
       </c>
       <c r="H6" s="1">
-        <v>47.22</v>
+        <v>38.89</v>
       </c>
       <c r="I6" s="2">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>36.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
@@ -522,25 +522,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G2" s="1">
-        <v>67.65000000000001</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>32.35</v>
+        <v>14.71</v>
       </c>
       <c r="I2" s="2">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>32.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -557,25 +557,25 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>64.70999999999999</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>35.29</v>
+        <v>17.65</v>
       </c>
       <c r="I3" s="2">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>35.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -959,25 +959,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>67.65000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>32.35</v>
+        <v>11.76</v>
       </c>
       <c r="I2" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>32.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -994,25 +994,25 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>64.70999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>35.29</v>
+        <v>14.71</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>35.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1396,25 +1396,25 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>67.65000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>32.35</v>
+        <v>11.76</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="J2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>32.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1431,25 +1431,25 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>64.70999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>35.29</v>
+        <v>14.71</v>
       </c>
       <c r="I3" s="2">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>35.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
@@ -849,13 +849,13 @@
         <v>28.21</v>
       </c>
       <c r="I11" s="2">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>28.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1274,25 +1274,25 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>69.23</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>30.77</v>
+        <v>10.26</v>
       </c>
       <c r="I11" s="2">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J11">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>28.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1711,25 +1711,25 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F11">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>69.23</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>30.77</v>
+        <v>10.26</v>
       </c>
       <c r="I11" s="2">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J11">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>28.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
@@ -1099,19 +1099,19 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
-        <v>61.11</v>
+        <v>66.67</v>
       </c>
       <c r="H6" s="1">
-        <v>38.89</v>
+        <v>33.33</v>
       </c>
       <c r="I6" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1536,19 +1536,19 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
-        <v>61.11</v>
+        <v>66.67</v>
       </c>
       <c r="H6" s="1">
-        <v>38.89</v>
+        <v>33.33</v>
       </c>
       <c r="I6" s="2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J6">
         <v>0</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
@@ -1396,16 +1396,16 @@
         <v>34</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H2" s="1">
-        <v>11.76</v>
+        <v>5.88</v>
       </c>
       <c r="I2" s="2">
         <v>8.1</v>
@@ -1431,16 +1431,16 @@
         <v>34</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>85.29000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="H3" s="1">
-        <v>14.71</v>
+        <v>5.88</v>
       </c>
       <c r="I3" s="2">
         <v>8.199999999999999</v>
@@ -1711,16 +1711,16 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>89.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H11" s="1">
-        <v>10.26</v>
+        <v>7.69</v>
       </c>
       <c r="I11" s="2">
         <v>8.300000000000001</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
@@ -1466,19 +1466,19 @@
         <v>41</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1">
-        <v>78.05</v>
+        <v>70.73</v>
       </c>
       <c r="H4" s="1">
-        <v>21.95</v>
+        <v>29.27</v>
       </c>
       <c r="I4" s="2">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
-        <v>82.5</v>
+        <v>75</v>
       </c>
       <c r="H5" s="1">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="I5" s="2">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1536,19 +1536,19 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H6" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
       <c r="I6" s="2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1571,19 +1571,19 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I7" s="2">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1606,16 +1606,16 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>95.45</v>
+        <v>97.73</v>
       </c>
       <c r="H8" s="1">
-        <v>4.55</v>
+        <v>2.27</v>
       </c>
       <c r="I8" s="2">
         <v>9.1</v>
@@ -1641,19 +1641,19 @@
         <v>43</v>
       </c>
       <c r="E9">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>100</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="I9" s="2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1688,7 +1688,7 @@
         <v>2.33</v>
       </c>
       <c r="I10" s="2">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
@@ -1746,19 +1746,19 @@
         <v>30</v>
       </c>
       <c r="E12">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>86.67</v>
+        <v>80</v>
       </c>
       <c r="H12" s="1">
-        <v>13.33</v>
+        <v>20</v>
       </c>
       <c r="I12" s="2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
+++ b/academias/Lectura, Expresión Oral y Escrita - Estadisticos 20221.xlsx
@@ -1309,25 +1309,25 @@
         <v>30</v>
       </c>
       <c r="E12">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>80</v>
+        <v>86.67</v>
       </c>
       <c r="H12" s="1">
-        <v>20</v>
+        <v>13.33</v>
       </c>
       <c r="I12" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
